--- a/data/Escenarios_DCH_septiembre/Bateria_353/Costo_fijo/Carga_on_board_fixed_3estaciones_P160kW/elmo_data.xlsx
+++ b/data/Escenarios_DCH_septiembre/Bateria_353/Costo_fijo/Carga_on_board_fixed_3estaciones_P160kW/elmo_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\TECNO-MASTER\Desktop\Elmo_infrastructure_sizing_NP-\data\Escenarios_DCH_septiembre\Bateria_353\Costo_fijo\Carga_on_board_fixed_3estaciones_P160kW\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBDDF3ED-8308-4BE2-95F2-0385073CD46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC5AC37-7438-4EAD-AF86-AC8B17B7BE42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3840" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LHD" sheetId="2" r:id="rId1"/>
@@ -1568,7 +1568,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1762,6 +1762,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2095,7 +2102,7 @@
     <col min="25" max="25" width="20.140625" style="22" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="13.5703125" style="22" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="8.42578125" style="22" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="17" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="17" style="69" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="19.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2181,7 +2188,7 @@
       <c r="AA1" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="24" t="s">
+      <c r="AB1" s="67" t="s">
         <v>27</v>
       </c>
       <c r="AC1" s="24" t="s">
@@ -2270,7 +2277,7 @@
       <c r="AA2" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="AB2" s="24" t="s">
+      <c r="AB2" s="67" t="s">
         <v>37</v>
       </c>
       <c r="AC2" s="24" t="s">
@@ -2359,10 +2366,10 @@
       <c r="AA3" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB3" s="7">
+      <c r="AB3" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC3" s="7">
+      <c r="AC3" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -2448,10 +2455,10 @@
       <c r="AA4" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB4" s="7">
+      <c r="AB4" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC4" s="7">
+      <c r="AC4" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -2537,10 +2544,10 @@
       <c r="AA5" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB5" s="7">
+      <c r="AB5" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC5" s="7">
+      <c r="AC5" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -2626,10 +2633,10 @@
       <c r="AA6" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB6" s="7">
+      <c r="AB6" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC6" s="7">
+      <c r="AC6" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -2715,10 +2722,10 @@
       <c r="AA7" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB7" s="7">
+      <c r="AB7" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC7" s="7">
+      <c r="AC7" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -2804,10 +2811,10 @@
       <c r="AA8" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB8" s="7">
+      <c r="AB8" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC8" s="7">
+      <c r="AC8" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -2893,10 +2900,10 @@
       <c r="AA9" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB9" s="7">
+      <c r="AB9" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC9" s="7">
+      <c r="AC9" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -2982,10 +2989,10 @@
       <c r="AA10" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB10" s="7">
+      <c r="AB10" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC10" s="7">
+      <c r="AC10" s="68">
         <v>0.95</v>
       </c>
     </row>
@@ -3071,10 +3078,10 @@
       <c r="AA11" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB11" s="7">
+      <c r="AB11" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC11" s="7">
+      <c r="AC11" s="68">
         <v>0.95</v>
       </c>
       <c r="AD11"/>
@@ -3206,10 +3213,10 @@
       <c r="AA12" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB12" s="7">
+      <c r="AB12" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC12" s="7">
+      <c r="AC12" s="68">
         <v>0.95</v>
       </c>
       <c r="AD12"/>
@@ -3341,10 +3348,10 @@
       <c r="AA13" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB13" s="7">
+      <c r="AB13" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC13" s="7">
+      <c r="AC13" s="68">
         <v>0.95</v>
       </c>
       <c r="AD13"/>
@@ -3476,10 +3483,10 @@
       <c r="AA14" s="7">
         <v>0.2</v>
       </c>
-      <c r="AB14" s="7">
+      <c r="AB14" s="68">
         <v>0.95</v>
       </c>
-      <c r="AC14" s="7">
+      <c r="AC14" s="68">
         <v>0.95</v>
       </c>
       <c r="AD14"/>
